--- a/research/traditional_assets/database/data/bulgaria/bulgaria_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.603</v>
+        <v>0.2078</v>
       </c>
       <c r="E2">
-        <v>0.3905</v>
+        <v>0.321</v>
       </c>
       <c r="G2">
-        <v>0.1342756183745583</v>
+        <v>0.01904103563124489</v>
       </c>
       <c r="H2">
-        <v>0.1342756183745583</v>
+        <v>0.01904103563124489</v>
       </c>
       <c r="I2">
-        <v>0.3526838297156319</v>
+        <v>0.2001927145520434</v>
       </c>
       <c r="J2">
-        <v>0.3437001758249262</v>
+        <v>0.1959732681068696</v>
       </c>
       <c r="K2">
-        <v>3.411</v>
+        <v>8.905000000000001</v>
       </c>
       <c r="L2">
-        <v>0.5739525492175669</v>
+        <v>0.1865351180376632</v>
       </c>
       <c r="M2">
-        <v>0.083</v>
+        <v>0.46</v>
       </c>
       <c r="N2">
-        <v>0.00114530150407065</v>
+        <v>0.002241125629707581</v>
       </c>
       <c r="O2">
-        <v>0.02433304016417473</v>
+        <v>0.05165637282425602</v>
       </c>
       <c r="P2">
-        <v>0.083</v>
+        <v>0.46</v>
       </c>
       <c r="Q2">
-        <v>0.00114530150407065</v>
+        <v>0.002241125629707581</v>
       </c>
       <c r="R2">
-        <v>0.02433304016417473</v>
+        <v>0.05165637282425602</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5.507</v>
+        <v>11.522</v>
       </c>
       <c r="V2">
-        <v>0.07599006485442251</v>
+        <v>0.05613532501193642</v>
       </c>
       <c r="W2">
-        <v>0.06366109133826323</v>
+        <v>-0.01701298701298701</v>
       </c>
       <c r="X2">
-        <v>0.05523202701522469</v>
+        <v>0.08815321808178633</v>
       </c>
       <c r="Y2">
-        <v>0.008429064323038533</v>
+        <v>-0.1051662050947733</v>
       </c>
       <c r="Z2">
-        <v>0.06304633794449631</v>
+        <v>0.1568401340429726</v>
       </c>
       <c r="AA2">
-        <v>0.02465885326341527</v>
+        <v>0.002682280592718589</v>
       </c>
       <c r="AB2">
-        <v>0.05523202701522469</v>
+        <v>0.08815321808178633</v>
       </c>
       <c r="AC2">
-        <v>-0.0387456618155917</v>
+        <v>-0.105818824826092</v>
       </c>
       <c r="AD2">
-        <v>73.7</v>
+        <v>184</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>73.7</v>
+        <v>184</v>
       </c>
       <c r="AG2">
-        <v>68.193</v>
+        <v>172.478</v>
       </c>
       <c r="AH2">
-        <v>0.5042074297051378</v>
+        <v>0.4726990602537161</v>
       </c>
       <c r="AI2">
-        <v>0.5737641105488518</v>
+        <v>0.5076870440473694</v>
       </c>
       <c r="AJ2">
-        <v>0.4847969970781228</v>
+        <v>0.4566147427276482</v>
       </c>
       <c r="AK2">
-        <v>0.5546716771186647</v>
+        <v>0.4915219460482295</v>
       </c>
       <c r="AL2">
-        <v>3.001</v>
+        <v>6.643999999999999</v>
       </c>
       <c r="AM2">
-        <v>0.1110000000000002</v>
+        <v>3.420999999999999</v>
       </c>
       <c r="AN2">
-        <v>58.1230283911672</v>
+        <v>35.81159984429739</v>
       </c>
       <c r="AO2">
-        <v>0.6984338553815396</v>
+        <v>1.438440698374474</v>
       </c>
       <c r="AP2">
-        <v>53.77996845425867</v>
+        <v>33.5690930323083</v>
       </c>
       <c r="AQ2">
-        <v>18.88288288288285</v>
+        <v>2.793627594270682</v>
       </c>
     </row>
     <row r="3">
@@ -728,64 +728,67 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.8775510204081634</v>
+        <v>0.9774436090225563</v>
       </c>
       <c r="J3">
-        <v>0.8699201419698316</v>
+        <v>0.8744360902255638</v>
       </c>
       <c r="K3">
-        <v>1.14</v>
+        <v>6.98</v>
       </c>
       <c r="L3">
-        <v>0.7755102040816326</v>
+        <v>0.87468671679198</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.46</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.01722846441947565</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.0659025787965616</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.46</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.01722846441947565</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.0659025787965616</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>0.505</v>
+        <v>0.284</v>
       </c>
       <c r="V3">
-        <v>0.01525679758308157</v>
+        <v>0.01063670411985019</v>
       </c>
       <c r="W3">
-        <v>0.1578947368421053</v>
+        <v>0.8440145102781138</v>
       </c>
       <c r="X3">
-        <v>0.05523202701522469</v>
+        <v>0.08815321808178633</v>
       </c>
       <c r="Y3">
-        <v>0.1026627098268806</v>
+        <v>0.7558612921963275</v>
       </c>
       <c r="Z3">
-        <v>0.2324110671936759</v>
+        <v>1.027688345138442</v>
       </c>
       <c r="AA3">
-        <v>0.2021790685684826</v>
+        <v>0.8986477784932388</v>
       </c>
       <c r="AB3">
-        <v>0.05523202701522469</v>
+        <v>0.08815321808178633</v>
       </c>
       <c r="AC3">
-        <v>0.1469470415532579</v>
+        <v>0.8104945604114525</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -797,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.505</v>
+        <v>-0.284</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -806,19 +809,19 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.01549317379966253</v>
+        <v>-0.01075105996365839</v>
       </c>
       <c r="AK3">
-        <v>-0.06503541532517708</v>
+        <v>-0.02198823165066584</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.03</v>
+        <v>-0.013</v>
       </c>
       <c r="AQ3">
-        <v>-43</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bulgarian Private Equity Fund AD (BUL:BPEF)</t>
+          <t>Holding Varna PLC (BUL:HVAR)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -837,8 +840,11 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.0436</v>
+      </c>
       <c r="E4">
-        <v>0.5670000000000001</v>
+        <v>0.321</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -847,103 +853,106 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.7844827586206897</v>
+        <v>0.04587912087912088</v>
       </c>
       <c r="J4">
-        <v>0.7517959770114944</v>
+        <v>0.04587912087912088</v>
       </c>
       <c r="K4">
-        <v>0.207</v>
+        <v>2.48</v>
       </c>
       <c r="L4">
-        <v>0.5948275862068966</v>
+        <v>0.06813186813186814</v>
       </c>
       <c r="M4">
-        <v>0.083</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.005608108108108108</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.4009661835748793</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>0.083</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.005608108108108108</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.4009661835748793</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>3.48</v>
+        <v>9.93</v>
       </c>
       <c r="V4">
-        <v>0.2351351351351351</v>
+        <v>0.06456436931079323</v>
       </c>
       <c r="W4">
-        <v>0.02684824902723735</v>
+        <v>0.02220232766338406</v>
       </c>
       <c r="X4">
-        <v>0.05523202701522469</v>
+        <v>0.1224918908186651</v>
       </c>
       <c r="Y4">
-        <v>-0.02838377798798734</v>
+        <v>-0.100289563155281</v>
       </c>
       <c r="Z4">
-        <v>0.05594855305466238</v>
+        <v>0.1778646469582214</v>
       </c>
       <c r="AA4">
-        <v>0.04206189710610934</v>
+        <v>0.008160273637918396</v>
       </c>
       <c r="AB4">
-        <v>0.05523202701522469</v>
+        <v>0.09531978654038163</v>
       </c>
       <c r="AC4">
-        <v>-0.01317012990911536</v>
+        <v>-0.08715951290246324</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>118.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>118.9</v>
       </c>
       <c r="AG4">
-        <v>-3.48</v>
+        <v>108.97</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.436010267693436</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.4694038689301224</v>
       </c>
       <c r="AJ4">
-        <v>-0.3074204946996466</v>
+        <v>0.4146972637667923</v>
       </c>
       <c r="AK4">
-        <v>-0.3733905579399142</v>
+        <v>0.4477544479598964</v>
       </c>
       <c r="AL4">
-        <v>0.001</v>
+        <v>3.82</v>
       </c>
       <c r="AM4">
-        <v>0.001</v>
+        <v>2.48</v>
+      </c>
+      <c r="AN4">
+        <v>26.07456140350877</v>
       </c>
       <c r="AO4">
-        <v>273</v>
+        <v>0.4371727748691099</v>
+      </c>
+      <c r="AP4">
+        <v>23.8969298245614</v>
       </c>
       <c r="AQ4">
-        <v>273</v>
+        <v>0.6733870967741936</v>
       </c>
     </row>
     <row r="5">
@@ -963,28 +972,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.603</v>
-      </c>
-      <c r="E5">
-        <v>0.214</v>
+        <v>0.3720000000000001</v>
       </c>
       <c r="G5">
-        <v>0.215158924205379</v>
+        <v>0.2713432835820895</v>
       </c>
       <c r="H5">
-        <v>0.215158924205379</v>
+        <v>0.2713432835820895</v>
       </c>
       <c r="I5">
-        <v>0.1506112469437653</v>
+        <v>0.07343283582089552</v>
       </c>
       <c r="J5">
-        <v>0.1428507437615484</v>
+        <v>0.07343283582089552</v>
       </c>
       <c r="K5">
-        <v>2.12</v>
+        <v>-0.393</v>
       </c>
       <c r="L5">
-        <v>0.5183374083129585</v>
+        <v>-0.1173134328358209</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -993,7 +999,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1002,79 +1008,79 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.9370000000000001</v>
+        <v>0.455</v>
       </c>
       <c r="V5">
-        <v>0.04440758293838862</v>
+        <v>0.0220873786407767</v>
       </c>
       <c r="W5">
-        <v>0.1004739336492891</v>
+        <v>-0.01701298701298701</v>
       </c>
       <c r="X5">
-        <v>0.1813911432199571</v>
+        <v>0.2285223951406145</v>
       </c>
       <c r="Y5">
-        <v>-0.08091720957066802</v>
+        <v>-0.2455353821536015</v>
       </c>
       <c r="Z5">
-        <v>0.05079294114724985</v>
+        <v>0.03652699181141168</v>
       </c>
       <c r="AA5">
-        <v>0.007255809420721196</v>
+        <v>0.002682280592718589</v>
       </c>
       <c r="AB5">
-        <v>0.07157700314278924</v>
+        <v>0.1085011054188106</v>
       </c>
       <c r="AC5">
-        <v>-0.06432119372206804</v>
+        <v>-0.105818824826092</v>
       </c>
       <c r="AD5">
-        <v>73.7</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>73.7</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="AG5">
-        <v>72.76300000000001</v>
+        <v>64.645</v>
       </c>
       <c r="AH5">
-        <v>0.7774261603375526</v>
+        <v>0.7596266044340724</v>
       </c>
       <c r="AI5">
-        <v>0.7052631578947368</v>
+        <v>0.7083786724700761</v>
       </c>
       <c r="AJ5">
-        <v>0.775204287099283</v>
+        <v>0.7583435978649773</v>
       </c>
       <c r="AK5">
-        <v>0.7025964871624036</v>
+        <v>0.7069276614358357</v>
       </c>
       <c r="AL5">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="AM5">
-        <v>0.1400000000000001</v>
+        <v>0.9499999999999997</v>
       </c>
       <c r="AN5">
-        <v>54.59259259259259</v>
+        <v>112.6297577854671</v>
       </c>
       <c r="AO5">
-        <v>0.2053333333333333</v>
+        <v>0.08723404255319149</v>
       </c>
       <c r="AP5">
-        <v>53.89851851851852</v>
+        <v>111.8425605536332</v>
       </c>
       <c r="AQ5">
-        <v>4.399999999999996</v>
+        <v>0.2589473684210527</v>
       </c>
     </row>
     <row r="6">
@@ -1085,7 +1091,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Real Bulland JSC (BUL:RBL)</t>
+          <t>Compass Receivable Fund Reit (BUL:CRF)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1094,22 +1100,22 @@
         </is>
       </c>
       <c r="G6">
-        <v>-2.342857142857143</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>-2.342857142857143</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>-2.371428571428571</v>
+        <v>-4.333333333333334</v>
       </c>
       <c r="J6">
-        <v>-2.371428571428571</v>
+        <v>-4.333333333333334</v>
       </c>
       <c r="K6">
-        <v>-0.056</v>
+        <v>-0.041</v>
       </c>
       <c r="L6">
-        <v>-1.6</v>
+        <v>-4.555555555555556</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1133,31 +1139,31 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.585</v>
+        <v>0.758</v>
       </c>
       <c r="V6">
-        <v>0.1685878962536023</v>
+        <v>0.8875878220140515</v>
       </c>
       <c r="W6">
-        <v>-0.0448</v>
+        <v>-0.04767441860465117</v>
       </c>
       <c r="X6">
-        <v>0.05523202701522469</v>
+        <v>0.08815321808178633</v>
       </c>
       <c r="Y6">
-        <v>-0.1000320270152247</v>
+        <v>-0.1358276366864375</v>
       </c>
       <c r="Z6">
-        <v>0.02926421404682275</v>
+        <v>0.03571428571428571</v>
       </c>
       <c r="AA6">
-        <v>-0.0693979933110368</v>
+        <v>-0.1547619047619048</v>
       </c>
       <c r="AB6">
-        <v>0.05523202701522469</v>
+        <v>0.08815321808178633</v>
       </c>
       <c r="AC6">
-        <v>-0.1246300203262615</v>
+        <v>-0.2429151228436911</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1169,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>-0.585</v>
+        <v>-0.758</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -1178,10 +1184,7 @@
         <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-0.2027729636048527</v>
-      </c>
-      <c r="AK6">
-        <v>-0.2549019607843137</v>
+        <v>-7.895833333333336</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1189,11 +1192,94 @@
       <c r="AM6">
         <v>0</v>
       </c>
-      <c r="AN6">
-        <v>-0</v>
-      </c>
-      <c r="AP6">
-        <v>7.134146341463414</v>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ImPulse I AD (BUL:IMP)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K7">
+        <v>-0.121</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0.095</v>
+      </c>
+      <c r="V7">
+        <v>0.02878787878787879</v>
+      </c>
+      <c r="X7">
+        <v>0.08815321808178633</v>
+      </c>
+      <c r="AB7">
+        <v>0.08815321808178633</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>-0.095</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.0296411856474259</v>
+      </c>
+      <c r="AK7">
+        <v>-0.02992125984251969</v>
+      </c>
+      <c r="AL7">
+        <v>0.004</v>
+      </c>
+      <c r="AM7">
+        <v>0.004</v>
+      </c>
+      <c r="AO7">
+        <v>-30</v>
+      </c>
+      <c r="AQ7">
+        <v>-30</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bulgaria/bulgaria_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.2078</v>
+        <v>-0.02285</v>
       </c>
       <c r="E2">
-        <v>0.321</v>
+        <v>-0.01015</v>
       </c>
       <c r="G2">
-        <v>0.01904103563124489</v>
+        <v>0.1184636197870713</v>
       </c>
       <c r="H2">
-        <v>0.01904103563124489</v>
+        <v>0.1184636197870713</v>
       </c>
       <c r="I2">
-        <v>0.2001927145520434</v>
+        <v>0.1710095484579338</v>
       </c>
       <c r="J2">
-        <v>0.1959732681068696</v>
+        <v>0.1532809676182086</v>
       </c>
       <c r="K2">
-        <v>8.905000000000001</v>
+        <v>7.355</v>
       </c>
       <c r="L2">
-        <v>0.1865351180376632</v>
+        <v>0.1442072034978334</v>
       </c>
       <c r="M2">
-        <v>0.46</v>
+        <v>0.404</v>
       </c>
       <c r="N2">
-        <v>0.002241125629707581</v>
+        <v>0.001850155706173292</v>
       </c>
       <c r="O2">
-        <v>0.05165637282425602</v>
+        <v>0.05492861998640381</v>
       </c>
       <c r="P2">
-        <v>0.46</v>
+        <v>0.404</v>
       </c>
       <c r="Q2">
-        <v>0.002241125629707581</v>
+        <v>0.001850155706173292</v>
       </c>
       <c r="R2">
-        <v>0.05165637282425602</v>
+        <v>0.05492861998640381</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>11.522</v>
+        <v>8.724</v>
       </c>
       <c r="V2">
-        <v>0.05613532501193642</v>
+        <v>0.03995237222934604</v>
       </c>
       <c r="W2">
-        <v>-0.01701298701298701</v>
+        <v>0.07944871476981569</v>
       </c>
       <c r="X2">
-        <v>0.08815321808178633</v>
+        <v>0.08503498267073277</v>
       </c>
       <c r="Y2">
-        <v>-0.1051662050947733</v>
+        <v>-0.005586267900917083</v>
       </c>
       <c r="Z2">
-        <v>0.1568401340429726</v>
+        <v>0.1759142692571681</v>
       </c>
       <c r="AA2">
-        <v>0.002682280592718589</v>
+        <v>0.01198790856495714</v>
       </c>
       <c r="AB2">
-        <v>0.08815321808178633</v>
+        <v>0.07705082957341833</v>
       </c>
       <c r="AC2">
-        <v>-0.105818824826092</v>
+        <v>-0.0693185844597641</v>
       </c>
       <c r="AD2">
-        <v>184</v>
+        <v>203.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>184</v>
+        <v>203.2</v>
       </c>
       <c r="AG2">
-        <v>172.478</v>
+        <v>194.476</v>
       </c>
       <c r="AH2">
-        <v>0.4726990602537161</v>
+        <v>0.4820191669038808</v>
       </c>
       <c r="AI2">
-        <v>0.5076870440473694</v>
+        <v>0.5255942681255011</v>
       </c>
       <c r="AJ2">
-        <v>0.4566147427276482</v>
+        <v>0.4710732591149996</v>
       </c>
       <c r="AK2">
-        <v>0.4915219460482295</v>
+        <v>0.5146419819733994</v>
       </c>
       <c r="AL2">
-        <v>6.643999999999999</v>
+        <v>7.786</v>
       </c>
       <c r="AM2">
-        <v>3.420999999999999</v>
+        <v>4.906</v>
       </c>
       <c r="AN2">
-        <v>35.81159984429739</v>
+        <v>43.75538329026701</v>
       </c>
       <c r="AO2">
-        <v>1.438440698374474</v>
+        <v>1.120215771898279</v>
       </c>
       <c r="AP2">
-        <v>33.5690930323083</v>
+        <v>41.87683031869079</v>
       </c>
       <c r="AQ2">
-        <v>2.793627594270682</v>
+        <v>1.777823073787199</v>
       </c>
     </row>
     <row r="3">
@@ -722,40 +722,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.2868988391376451</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.2868988391376451</v>
       </c>
       <c r="I3">
-        <v>0.9774436090225563</v>
+        <v>0.9684908789386401</v>
       </c>
       <c r="J3">
-        <v>0.8744360902255638</v>
+        <v>0.9349917081260364</v>
       </c>
       <c r="K3">
-        <v>6.98</v>
+        <v>5.64</v>
       </c>
       <c r="L3">
-        <v>0.87468671679198</v>
+        <v>0.9353233830845771</v>
       </c>
       <c r="M3">
-        <v>0.46</v>
+        <v>0.372</v>
       </c>
       <c r="N3">
-        <v>0.01722846441947565</v>
+        <v>0.01506072874493927</v>
       </c>
       <c r="O3">
-        <v>0.0659025787965616</v>
+        <v>0.06595744680851064</v>
       </c>
       <c r="P3">
-        <v>0.46</v>
+        <v>0.372</v>
       </c>
       <c r="Q3">
-        <v>0.01722846441947565</v>
+        <v>0.01506072874493927</v>
       </c>
       <c r="R3">
-        <v>0.0659025787965616</v>
+        <v>0.06595744680851064</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,31 +764,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.284</v>
+        <v>0.494</v>
       </c>
       <c r="V3">
-        <v>0.01063670411985019</v>
+        <v>0.02</v>
       </c>
       <c r="W3">
-        <v>0.8440145102781138</v>
+        <v>0.4272727272727272</v>
       </c>
       <c r="X3">
-        <v>0.08815321808178633</v>
+        <v>0.07425542537476212</v>
       </c>
       <c r="Y3">
-        <v>0.7558612921963275</v>
+        <v>0.3530173018979651</v>
       </c>
       <c r="Z3">
-        <v>1.027688345138442</v>
+        <v>0.466862805822236</v>
       </c>
       <c r="AA3">
-        <v>0.8986477784932388</v>
+        <v>0.4365128522762465</v>
       </c>
       <c r="AB3">
-        <v>0.08815321808178633</v>
+        <v>0.07425542537476212</v>
       </c>
       <c r="AC3">
-        <v>0.8104945604114525</v>
+        <v>0.3622574269014844</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.284</v>
+        <v>-0.494</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -809,19 +809,19 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.01075105996365839</v>
+        <v>-0.02040816326530612</v>
       </c>
       <c r="AK3">
-        <v>-0.02198823165066584</v>
+        <v>-0.02612927113085793</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.013</v>
+        <v>-0.002</v>
       </c>
       <c r="AQ3">
-        <v>-600</v>
+        <v>-2920</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Holding Varna PLC (BUL:HVAR)</t>
+          <t>ImPulse I AD (BUL:IMP)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -840,12 +840,6 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.0436</v>
-      </c>
-      <c r="E4">
-        <v>0.321</v>
-      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -853,16 +847,16 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.04587912087912088</v>
+        <v>0.8696682464454977</v>
       </c>
       <c r="J4">
-        <v>0.04587912087912088</v>
+        <v>0.7936316784502629</v>
       </c>
       <c r="K4">
-        <v>2.48</v>
+        <v>0.334</v>
       </c>
       <c r="L4">
-        <v>0.06813186813186814</v>
+        <v>0.7914691943127963</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -886,73 +880,67 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>9.93</v>
+        <v>0.242</v>
       </c>
       <c r="V4">
-        <v>0.06456436931079323</v>
+        <v>0.05748218527315915</v>
       </c>
       <c r="W4">
-        <v>0.02220232766338406</v>
+        <v>0.1021406727828746</v>
       </c>
       <c r="X4">
-        <v>0.1224918908186651</v>
+        <v>0.07425542537476212</v>
       </c>
       <c r="Y4">
-        <v>-0.100289563155281</v>
+        <v>0.0278852474081125</v>
       </c>
       <c r="Z4">
-        <v>0.1778646469582214</v>
+        <v>0.1329133858267716</v>
       </c>
       <c r="AA4">
-        <v>0.008160273637918396</v>
+        <v>0.1054842734822082</v>
       </c>
       <c r="AB4">
-        <v>0.09531978654038163</v>
+        <v>0.07425542537476212</v>
       </c>
       <c r="AC4">
-        <v>-0.08715951290246324</v>
+        <v>0.03122884810744604</v>
       </c>
       <c r="AD4">
-        <v>118.9</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>118.9</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>108.97</v>
+        <v>-0.242</v>
       </c>
       <c r="AH4">
-        <v>0.436010267693436</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.4694038689301224</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.4146972637667923</v>
+        <v>-0.06098790322580645</v>
       </c>
       <c r="AK4">
-        <v>0.4477544479598964</v>
+        <v>-0.06898517673888255</v>
       </c>
       <c r="AL4">
-        <v>3.82</v>
+        <v>0.001</v>
       </c>
       <c r="AM4">
-        <v>2.48</v>
-      </c>
-      <c r="AN4">
-        <v>26.07456140350877</v>
+        <v>0.001</v>
       </c>
       <c r="AO4">
-        <v>0.4371727748691099</v>
-      </c>
-      <c r="AP4">
-        <v>23.8969298245614</v>
+        <v>367</v>
       </c>
       <c r="AQ4">
-        <v>0.6733870967741936</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5">
@@ -963,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Holding Sveta Sofia AD (BUL:HSOF)</t>
+          <t>Real Bulland AD (BUL:RBL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -972,115 +960,112 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.3720000000000001</v>
+        <v>0.408</v>
       </c>
       <c r="G5">
-        <v>0.2713432835820895</v>
+        <v>0.1219512195121951</v>
       </c>
       <c r="H5">
-        <v>0.2713432835820895</v>
+        <v>0.1219512195121951</v>
       </c>
       <c r="I5">
-        <v>0.07343283582089552</v>
+        <v>0.1707317073170732</v>
       </c>
       <c r="J5">
-        <v>0.07343283582089552</v>
+        <v>0.1707317073170732</v>
       </c>
       <c r="K5">
-        <v>-0.393</v>
+        <v>0.477</v>
       </c>
       <c r="L5">
-        <v>-0.1173134328358209</v>
+        <v>3.878048780487805</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>0.032</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.007582938388625593</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>0.06708595387840671</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>0.032</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.007582938388625593</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>0.06708595387840671</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>0.455</v>
+        <v>0.029</v>
       </c>
       <c r="V5">
-        <v>0.0220873786407767</v>
+        <v>0.006872037914691944</v>
       </c>
       <c r="W5">
-        <v>-0.01701298701298701</v>
+        <v>0.1558823529411765</v>
       </c>
       <c r="X5">
-        <v>0.2285223951406145</v>
+        <v>0.07425542537476212</v>
       </c>
       <c r="Y5">
-        <v>-0.2455353821536015</v>
+        <v>0.08162692756641435</v>
       </c>
       <c r="Z5">
-        <v>0.03652699181141168</v>
+        <v>0.04650283553875236</v>
       </c>
       <c r="AA5">
-        <v>0.002682280592718589</v>
+        <v>0.007939508506616257</v>
       </c>
       <c r="AB5">
-        <v>0.1085011054188106</v>
+        <v>0.07425542537476212</v>
       </c>
       <c r="AC5">
-        <v>-0.105818824826092</v>
+        <v>-0.06631591686814586</v>
       </c>
       <c r="AD5">
-        <v>65.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>65.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>64.645</v>
+        <v>-0.029</v>
       </c>
       <c r="AH5">
-        <v>0.7596266044340724</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.7083786724700761</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>0.7583435978649773</v>
+        <v>-0.006919589596754951</v>
       </c>
       <c r="AK5">
-        <v>0.7069276614358357</v>
+        <v>-0.007793603869927439</v>
       </c>
       <c r="AL5">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>0.9499999999999997</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>112.6297577854671</v>
-      </c>
-      <c r="AO5">
-        <v>0.08723404255319149</v>
+        <v>0</v>
       </c>
       <c r="AP5">
-        <v>111.8425605536332</v>
-      </c>
-      <c r="AQ5">
-        <v>0.2589473684210527</v>
+        <v>-1.380952380952381</v>
       </c>
     </row>
     <row r="6">
@@ -1091,7 +1076,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Compass Receivable Fund Reit (BUL:CRF)</t>
+          <t>Holding Varna AD (BUL:HVAR)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1099,23 +1084,29 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.0278</v>
+      </c>
+      <c r="E6">
+        <v>0.0216</v>
+      </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.1007462686567164</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.1007462686567164</v>
       </c>
       <c r="I6">
-        <v>-4.333333333333334</v>
+        <v>0.06144278606965174</v>
       </c>
       <c r="J6">
-        <v>-4.333333333333334</v>
+        <v>0.03072139303482587</v>
       </c>
       <c r="K6">
-        <v>-0.041</v>
+        <v>0.994</v>
       </c>
       <c r="L6">
-        <v>-4.555555555555556</v>
+        <v>0.02472636815920398</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1124,7 +1115,7 @@
         <v>-0</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1133,64 +1124,79 @@
         <v>-0</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.758</v>
+        <v>7.2</v>
       </c>
       <c r="V6">
-        <v>0.8875878220140515</v>
+        <v>0.045</v>
       </c>
       <c r="W6">
-        <v>-0.04767441860465117</v>
+        <v>0.01046315789473684</v>
       </c>
       <c r="X6">
-        <v>0.08815321808178633</v>
+        <v>0.09581453996670342</v>
       </c>
       <c r="Y6">
-        <v>-0.1358276366864375</v>
+        <v>-0.08535138207196658</v>
       </c>
       <c r="Z6">
-        <v>0.03571428571428571</v>
+        <v>0.2449427248354862</v>
       </c>
       <c r="AA6">
-        <v>-0.1547619047619048</v>
+        <v>0.007524981720692177</v>
       </c>
       <c r="AB6">
-        <v>0.08815321808178633</v>
+        <v>0.07984623377207452</v>
       </c>
       <c r="AC6">
-        <v>-0.2429151228436911</v>
+        <v>-0.07232125205138235</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>108.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>108.1</v>
       </c>
       <c r="AG6">
-        <v>-0.758</v>
+        <v>100.9</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.4032077582991421</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.4708188153310104</v>
       </c>
       <c r="AJ6">
-        <v>-7.895833333333336</v>
+        <v>0.3867382138750479</v>
+      </c>
+      <c r="AK6">
+        <v>0.4536870503597122</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>3.412</v>
+      </c>
+      <c r="AN6">
+        <v>21.237721021611</v>
+      </c>
+      <c r="AO6">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="AP6">
+        <v>19.82318271119843</v>
+      </c>
+      <c r="AQ6">
+        <v>0.7239155920281359</v>
       </c>
     </row>
     <row r="7">
@@ -1201,7 +1207,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ImPulse I AD (BUL:IMP)</t>
+          <t>Immovable Properties Sofia REIT Sofia (BUL:NIS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1209,8 +1215,29 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D7">
+        <v>-0.305</v>
+      </c>
+      <c r="E7">
+        <v>-0.04190000000000001</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0.5905292479108635</v>
+      </c>
+      <c r="J7">
+        <v>0.5905292479108635</v>
+      </c>
       <c r="K7">
-        <v>-0.121</v>
+        <v>0.462</v>
+      </c>
+      <c r="L7">
+        <v>0.6434540389972145</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1219,7 +1246,7 @@
         <v>-0</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1228,7 +1255,7 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1237,49 +1264,192 @@
         <v>0.095</v>
       </c>
       <c r="V7">
-        <v>0.02878787878787879</v>
+        <v>0.03242320819112628</v>
+      </c>
+      <c r="W7">
+        <v>0.05675675675675675</v>
       </c>
       <c r="X7">
-        <v>0.08815321808178633</v>
+        <v>0.2746451332949194</v>
+      </c>
+      <c r="Y7">
+        <v>-0.2178883765381626</v>
+      </c>
+      <c r="Z7">
+        <v>0.02715582450832072</v>
+      </c>
+      <c r="AA7">
+        <v>0.01603630862329803</v>
       </c>
       <c r="AB7">
-        <v>0.08815321808178633</v>
+        <v>0.0928009738187234</v>
+      </c>
+      <c r="AC7">
+        <v>-0.07676466519542538</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>18.4</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>18.4</v>
       </c>
       <c r="AG7">
-        <v>-0.095</v>
+        <v>18.305</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>0.8626347866854196</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>0.6940777065258393</v>
       </c>
       <c r="AJ7">
-        <v>-0.0296411856474259</v>
+        <v>0.8620202495879444</v>
       </c>
       <c r="AK7">
-        <v>-0.02992125984251969</v>
+        <v>0.6929774749195533</v>
       </c>
       <c r="AL7">
-        <v>0.004</v>
+        <v>0.535</v>
       </c>
       <c r="AM7">
-        <v>0.004</v>
+        <v>0.535</v>
       </c>
       <c r="AO7">
-        <v>-30</v>
+        <v>0.7925233644859813</v>
       </c>
       <c r="AQ7">
-        <v>-30</v>
+        <v>0.7925233644859813</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Holding Sveta Sofia AD (BUL:HSOF)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>-0.0735</v>
+      </c>
+      <c r="G8">
+        <v>0.07037037037037037</v>
+      </c>
+      <c r="H8">
+        <v>0.07037037037037037</v>
+      </c>
+      <c r="I8">
+        <v>-0.113960113960114</v>
+      </c>
+      <c r="J8">
+        <v>-0.113960113960114</v>
+      </c>
+      <c r="K8">
+        <v>-0.552</v>
+      </c>
+      <c r="L8">
+        <v>-0.1572649572649573</v>
+      </c>
+      <c r="M8">
+        <v>-0</v>
+      </c>
+      <c r="N8">
+        <v>-0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0.664</v>
+      </c>
+      <c r="V8">
+        <v>0.02977578475336323</v>
+      </c>
+      <c r="W8">
+        <v>-0.02860103626943005</v>
+      </c>
+      <c r="X8">
+        <v>0.1840082510976244</v>
+      </c>
+      <c r="Y8">
+        <v>-0.2126092873670545</v>
+      </c>
+      <c r="Z8">
+        <v>0.0435294847150741</v>
+      </c>
+      <c r="AA8">
+        <v>-0.004960625038754884</v>
+      </c>
+      <c r="AB8">
+        <v>0.09091150862868919</v>
+      </c>
+      <c r="AC8">
+        <v>-0.09587213366744407</v>
+      </c>
+      <c r="AD8">
+        <v>76.7</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>76.7</v>
+      </c>
+      <c r="AG8">
+        <v>76.036</v>
+      </c>
+      <c r="AH8">
+        <v>0.7747474747474747</v>
+      </c>
+      <c r="AI8">
+        <v>0.7403474903474904</v>
+      </c>
+      <c r="AJ8">
+        <v>0.7732264887731858</v>
+      </c>
+      <c r="AK8">
+        <v>0.7386725732493976</v>
+      </c>
+      <c r="AL8">
+        <v>3.26</v>
+      </c>
+      <c r="AM8">
+        <v>0.96</v>
+      </c>
+      <c r="AN8">
+        <v>-164.2398286937901</v>
+      </c>
+      <c r="AO8">
+        <v>-0.1226993865030675</v>
+      </c>
+      <c r="AP8">
+        <v>-162.8179871520342</v>
+      </c>
+      <c r="AQ8">
+        <v>-0.4166666666666667</v>
       </c>
     </row>
   </sheetData>
